--- a/2_Formulas_Functions/2_Functions_Intro.xlsx
+++ b/2_Formulas_Functions/2_Functions_Intro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\python\Excel_Data_Analytics\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB400695-7140-42BB-AAF4-BA859D4EE456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FAD6BE-57D8-49D6-A04B-B18B2B468695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="9" r:id="rId1"/>
@@ -1689,7 +1689,7 @@
         <v>119000</v>
       </c>
       <c r="E14" s="40">
-        <f t="shared" si="12"/>
+        <f>AVERAGE(E3:E12)</f>
         <v>10400</v>
       </c>
     </row>
